--- a/data/tier_app/country_costs.xlsx
+++ b/data/tier_app/country_costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/tier_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{A44B6979-C974-2F43-A899-180A4F7BAE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3C22998-F053-A14B-8830-DA286B7E3C1C}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{A44B6979-C974-2F43-A899-180A4F7BAE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C779809C-0E00-3141-AE3A-53E70C3E543B}"/>
   <bookViews>
-    <workbookView xWindow="440" yWindow="6620" windowWidth="27640" windowHeight="15280" xr2:uid="{A508B7DC-02AE-4845-B676-FDD92F1561DC}"/>
+    <workbookView xWindow="440" yWindow="1140" windowWidth="27640" windowHeight="15280" xr2:uid="{A508B7DC-02AE-4845-B676-FDD92F1561DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Zambia</t>
   </si>
@@ -83,17 +83,29 @@
     <t>Zimbabwe</t>
   </si>
   <si>
-    <t>art_cost_standard</t>
-  </si>
-  <si>
     <t>country</t>
+  </si>
+  <si>
+    <t>Cost of treatment</t>
+  </si>
+  <si>
+    <t>Botswana</t>
+  </si>
+  <si>
+    <t>C'ote d'ivoire</t>
+  </si>
+  <si>
+    <t>Nigeria</t>
+  </si>
+  <si>
+    <t>Tanzania</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -115,12 +127,6 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -183,8 +189,8 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -520,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F954A092-A5F1-D044-85EF-FAF8818A0818}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -529,10 +535,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17" x14ac:dyDescent="0.2">
@@ -607,7 +613,7 @@
         <v>101.9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
@@ -631,7 +637,7 @@
         <v>113.46</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
@@ -655,9 +661,49 @@
         <v>130.18</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+    <row r="17" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="4">
+        <v>221.82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="4">
+        <v>144.28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="4">
+        <v>151.94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="4">
+        <v>120.74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/tier_app/country_costs.xlsx
+++ b/data/tier_app/country_costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/tier_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{A44B6979-C974-2F43-A899-180A4F7BAE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C779809C-0E00-3141-AE3A-53E70C3E543B}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{A44B6979-C974-2F43-A899-180A4F7BAE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E746C9AC-21AC-9149-BBB5-DBFAF06F59FF}"/>
   <bookViews>
-    <workbookView xWindow="440" yWindow="1140" windowWidth="27640" windowHeight="15280" xr2:uid="{A508B7DC-02AE-4845-B676-FDD92F1561DC}"/>
+    <workbookView xWindow="1860" yWindow="600" windowWidth="27640" windowHeight="15280" xr2:uid="{A508B7DC-02AE-4845-B676-FDD92F1561DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -83,29 +83,29 @@
     <t>Zimbabwe</t>
   </si>
   <si>
+    <t>art_cost_standard</t>
+  </si>
+  <si>
     <t>country</t>
   </si>
   <si>
-    <t>Cost of treatment</t>
-  </si>
-  <si>
     <t>Botswana</t>
   </si>
   <si>
-    <t>C'ote d'ivoire</t>
-  </si>
-  <si>
     <t>Nigeria</t>
   </si>
   <si>
-    <t>Tanzania</t>
+    <t>United Republic of Tanzania</t>
+  </si>
+  <si>
+    <t>Côte d'Ivoire</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -127,6 +127,12 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -189,8 +195,8 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -535,10 +541,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17" x14ac:dyDescent="0.2">
@@ -669,9 +675,9 @@
         <v>221.82</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <v>144.28</v>
@@ -679,15 +685,15 @@
     </row>
     <row r="19" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4">
         <v>151.94</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="4">
         <v>120.74</v>

--- a/data/tier_app/country_costs.xlsx
+++ b/data/tier_app/country_costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/tier_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{A44B6979-C974-2F43-A899-180A4F7BAE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E746C9AC-21AC-9149-BBB5-DBFAF06F59FF}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{A44B6979-C974-2F43-A899-180A4F7BAE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D44340FC-02DC-884D-9B37-DA3F9066F93D}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="600" windowWidth="27640" windowHeight="15280" xr2:uid="{A508B7DC-02AE-4845-B676-FDD92F1561DC}"/>
+    <workbookView xWindow="1160" yWindow="600" windowWidth="27640" windowHeight="15280" xr2:uid="{A508B7DC-02AE-4845-B676-FDD92F1561DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -552,7 +552,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>115.03</v>
+        <v>150.03</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.2">
@@ -675,7 +675,7 @@
         <v>221.82</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>

--- a/data/tier_app/country_costs.xlsx
+++ b/data/tier_app/country_costs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/tier_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{A44B6979-C974-2F43-A899-180A4F7BAE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D44340FC-02DC-884D-9B37-DA3F9066F93D}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{A44B6979-C974-2F43-A899-180A4F7BAE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3799D745-7044-094A-8BD4-A94F9FEA0F32}"/>
   <bookViews>
     <workbookView xWindow="1160" yWindow="600" windowWidth="27640" windowHeight="15280" xr2:uid="{A508B7DC-02AE-4845-B676-FDD92F1561DC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Zambia</t>
   </si>
@@ -99,6 +99,33 @@
   </si>
   <si>
     <t>Côte d'Ivoire</t>
+  </si>
+  <si>
+    <t>cost_test_network</t>
+  </si>
+  <si>
+    <t>cost_test_facility_general</t>
+  </si>
+  <si>
+    <t>cost_test_index</t>
+  </si>
+  <si>
+    <t>cost_test_community</t>
+  </si>
+  <si>
+    <t>cost_test_kpsti</t>
+  </si>
+  <si>
+    <t>cost_hivst_facility</t>
+  </si>
+  <si>
+    <t>cost_hivst_community</t>
+  </si>
+  <si>
+    <t>cost_anc_hiv_testing</t>
+  </si>
+  <si>
+    <t>cost_pnc_hiv_testing</t>
   </si>
 </sst>
 </file>
@@ -532,184 +559,900 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F954A092-A5F1-D044-85EF-FAF8818A0818}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4">
         <v>150.03</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C2" s="1">
+        <v>2.4280712530000002</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1.9151412779999999</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1.9151412779999999</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2.4280712530000002</v>
+      </c>
+      <c r="G2" s="1">
+        <v>2.4280712530000002</v>
+      </c>
+      <c r="H2" s="1">
+        <v>3.0879888270000002</v>
+      </c>
+      <c r="I2" s="1">
+        <v>3.1524877149999999</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1.745331695</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.745331695</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="4">
         <v>139.44999999999999</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C3" s="1">
+        <v>4.3166339069999999</v>
+      </c>
+      <c r="D3" s="1">
+        <v>3.2087051600000001</v>
+      </c>
+      <c r="E3" s="1">
+        <v>3.2087051600000001</v>
+      </c>
+      <c r="F3" s="1">
+        <v>4.3166339069999999</v>
+      </c>
+      <c r="G3" s="1">
+        <v>4.3166339069999999</v>
+      </c>
+      <c r="H3" s="1">
+        <v>4.3500558659999999</v>
+      </c>
+      <c r="I3" s="1">
+        <v>4.4893734639999998</v>
+      </c>
+      <c r="J3" s="1">
+        <v>2.8419164619999999</v>
+      </c>
+      <c r="K3" s="1">
+        <v>2.8419164619999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="4">
         <v>156.12</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C4" s="1">
+        <v>5.6088083539999998</v>
+      </c>
+      <c r="D4" s="1">
+        <v>4.0937751840000001</v>
+      </c>
+      <c r="E4" s="1">
+        <v>4.0937751840000001</v>
+      </c>
+      <c r="F4" s="1">
+        <v>5.6088083539999998</v>
+      </c>
+      <c r="G4" s="1">
+        <v>5.6088083539999998</v>
+      </c>
+      <c r="H4" s="1">
+        <v>5.2135754189999997</v>
+      </c>
+      <c r="I4" s="1">
+        <v>5.4040847669999996</v>
+      </c>
+      <c r="J4" s="1">
+        <v>3.5922113019999999</v>
+      </c>
+      <c r="K4" s="1">
+        <v>3.5922113019999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="4">
         <v>114.98</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C5" s="1">
+        <v>2.4246437350000001</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1.912793612</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1.912793612</v>
+      </c>
+      <c r="F5" s="1">
+        <v>2.4246437350000001</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2.4246437350000001</v>
+      </c>
+      <c r="H5" s="1">
+        <v>3.085698324</v>
+      </c>
+      <c r="I5" s="1">
+        <v>3.1500614250000001</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1.743341523</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.743341523</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="4">
         <v>133.02000000000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C6" s="1">
+        <v>3.8196437350000001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2.868293612</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2.868293612</v>
+      </c>
+      <c r="F6" s="1">
+        <v>3.8196437350000001</v>
+      </c>
+      <c r="G6" s="1">
+        <v>3.8196437350000001</v>
+      </c>
+      <c r="H6" s="1">
+        <v>4.0179329609999996</v>
+      </c>
+      <c r="I6" s="1">
+        <v>4.1375614250000003</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2.5533415229999998</v>
+      </c>
+      <c r="K6" s="1">
+        <v>2.5533415229999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="4">
         <v>129.11000000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C7" s="1">
+        <v>3.5180221129999998</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2.6616990170000001</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2.6616990170000001</v>
+      </c>
+      <c r="F7" s="1">
+        <v>3.5180221129999998</v>
+      </c>
+      <c r="G7" s="1">
+        <v>3.5180221129999998</v>
+      </c>
+      <c r="H7" s="1">
+        <v>3.8163687149999999</v>
+      </c>
+      <c r="I7" s="1">
+        <v>3.9240479119999998</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2.3782063880000002</v>
+      </c>
+      <c r="K7" s="1">
+        <v>2.3782063880000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="4">
         <v>107.88</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C8" s="1">
+        <v>1.8762407860000001</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1.537167076</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1.537167076</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1.8762407860000001</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1.8762407860000001</v>
+      </c>
+      <c r="H8" s="1">
+        <v>2.7192178770000002</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2.7618550370000001</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1.424914005</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1.424914005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="4">
         <v>103.12</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C9" s="1">
+        <v>1.5060687960000001</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1.283619165</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1.283619165</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1.5060687960000001</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1.5060687960000001</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2.4718435749999998</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2.4998157249999999</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1.2099754300000001</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1.2099754300000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="4">
         <v>101.9</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C10" s="1">
+        <v>1.4135257990000001</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1.2202321869999999</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1.2202321869999999</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1.4135257990000001</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1.4135257990000001</v>
+      </c>
+      <c r="H10" s="1">
+        <v>2.41</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2.41</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1.1562407859999999</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1.1562407859999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="4">
         <v>101.9</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C11" s="1">
+        <v>1.4100982799999999</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1.217884521</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1.217884521</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1.4100982799999999</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1.4100982799999999</v>
+      </c>
+      <c r="H11" s="1">
+        <v>2.4077094969999999</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2.4318796069999999</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1.154250614</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1.154250614</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="4">
         <v>150.69999999999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C12" s="1">
+        <v>5.1872235870000001</v>
+      </c>
+      <c r="D12" s="1">
+        <v>3.8050122850000001</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3.8050122850000001</v>
+      </c>
+      <c r="F12" s="1">
+        <v>5.1872235870000001</v>
+      </c>
+      <c r="G12" s="1">
+        <v>5.1872235870000001</v>
+      </c>
+      <c r="H12" s="1">
+        <v>4.9318435750000003</v>
+      </c>
+      <c r="I12" s="1">
+        <v>5.1056511059999998</v>
+      </c>
+      <c r="J12" s="1">
+        <v>3.3474201469999998</v>
+      </c>
+      <c r="K12" s="1">
+        <v>3.3474201469999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="4">
         <v>113.46</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C13" s="1">
+        <v>2.3046805899999998</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1.830625307</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1.830625307</v>
+      </c>
+      <c r="F13" s="1">
+        <v>2.3046805899999998</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2.3046805899999998</v>
+      </c>
+      <c r="H13" s="1">
+        <v>3.0055307259999999</v>
+      </c>
+      <c r="I13" s="1">
+        <v>3.065141278</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1.673685504</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1.673685504</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="4">
         <v>166.1</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C14" s="1">
+        <v>6.152552</v>
+      </c>
+      <c r="D14" s="1">
+        <v>4.3928589999999996</v>
+      </c>
+      <c r="E14" s="1">
+        <v>4.3928589999999996</v>
+      </c>
+      <c r="F14" s="1">
+        <v>6.152552</v>
+      </c>
+      <c r="G14" s="1">
+        <v>6.152552</v>
+      </c>
+      <c r="H14" s="1">
+        <v>5.7289385470000003</v>
+      </c>
+      <c r="I14" s="1">
+        <v>5.95</v>
+      </c>
+      <c r="J14" s="1">
+        <v>3.8131740000000001</v>
+      </c>
+      <c r="K14" s="1">
+        <v>3.8131740000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="4">
         <v>112.29</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C15" s="1">
+        <v>2.2155651110000001</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1.7695859949999999</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1.7695859949999999</v>
+      </c>
+      <c r="F15" s="1">
+        <v>2.2155651110000001</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2.2155651110000001</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2.945977654</v>
+      </c>
+      <c r="I15" s="1">
+        <v>3.0020577400000001</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1.6219410320000001</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1.6219410320000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="4">
         <v>130.18</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C16" s="1">
+        <v>3.6002825550000002</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2.718042998</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2.718042998</v>
+      </c>
+      <c r="F16" s="1">
+        <v>3.6002825550000002</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3.6002825550000002</v>
+      </c>
+      <c r="H16" s="1">
+        <v>3.8713407819999999</v>
+      </c>
+      <c r="I16" s="1">
+        <v>3.98227887</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2.425970516</v>
+      </c>
+      <c r="K16" s="1">
+        <v>2.425970516</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="4">
         <v>221.82</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C17" s="1">
+        <v>8.3542506139999997</v>
+      </c>
+      <c r="D17" s="1">
+        <v>5.9742555279999996</v>
+      </c>
+      <c r="E17" s="1">
+        <v>5.9742555279999996</v>
+      </c>
+      <c r="F17" s="1">
+        <v>8.3542506139999997</v>
+      </c>
+      <c r="G17" s="1">
+        <v>8.3542506139999997</v>
+      </c>
+      <c r="H17" s="1">
+        <v>7.0482681559999998</v>
+      </c>
+      <c r="I17" s="1">
+        <v>7.3475429979999998</v>
+      </c>
+      <c r="J17" s="1">
+        <v>5.1863390660000004</v>
+      </c>
+      <c r="K17" s="1">
+        <v>5.1863390660000004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="4">
         <v>144.28</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C18" s="1">
+        <v>3.7716584769999999</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2.83542629</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2.83542629</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3.7716584769999999</v>
+      </c>
+      <c r="G18" s="1">
+        <v>3.7716584769999999</v>
+      </c>
+      <c r="H18" s="1">
+        <v>3.9858659219999999</v>
+      </c>
+      <c r="I18" s="1">
+        <v>4.1035933660000001</v>
+      </c>
+      <c r="J18" s="1">
+        <v>2.525479115</v>
+      </c>
+      <c r="K18" s="1">
+        <v>2.525479115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="4">
         <v>151.94</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="C19" s="1">
+        <v>4.2240909090000001</v>
+      </c>
+      <c r="D19" s="1">
+        <v>3.145318182</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3.145318182</v>
+      </c>
+      <c r="F19" s="1">
+        <v>4.2240909090000001</v>
+      </c>
+      <c r="G19" s="1">
+        <v>4.2240909090000001</v>
+      </c>
+      <c r="H19" s="1">
+        <v>4.2882122909999998</v>
+      </c>
+      <c r="I19" s="1">
+        <v>4.4238636360000001</v>
+      </c>
+      <c r="J19" s="1">
+        <v>2.788181818</v>
+      </c>
+      <c r="K19" s="1">
+        <v>2.788181818</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="4">
         <v>120.74</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C20" s="1">
+        <v>2.380085995</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1.8822739559999999</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1.8822739559999999</v>
+      </c>
+      <c r="F20" s="1">
+        <v>2.380085995</v>
+      </c>
+      <c r="G20" s="1">
+        <v>2.380085995</v>
+      </c>
+      <c r="H20" s="1">
+        <v>3.055921788</v>
+      </c>
+      <c r="I20" s="1">
+        <v>3.1185196560000001</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1.7174692869999999</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1.7174692869999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/tier_app/country_costs.xlsx
+++ b/data/tier_app/country_costs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/tier_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{A44B6979-C974-2F43-A899-180A4F7BAE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3799D745-7044-094A-8BD4-A94F9FEA0F32}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="8_{A44B6979-C974-2F43-A899-180A4F7BAE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{973E1F22-1C3A-CF44-9E4C-A28B3EC62C24}"/>
   <bookViews>
     <workbookView xWindow="1160" yWindow="600" windowWidth="27640" windowHeight="15280" xr2:uid="{A508B7DC-02AE-4845-B676-FDD92F1561DC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Zambia</t>
   </si>
@@ -126,6 +126,30 @@
   </si>
   <si>
     <t>cost_pnc_hiv_testing</t>
+  </si>
+  <si>
+    <t>cost_prep_oral_agyw</t>
+  </si>
+  <si>
+    <t>cost_prep_oral_fsw</t>
+  </si>
+  <si>
+    <t>cost_prep_oral_msm</t>
+  </si>
+  <si>
+    <t>cost_prep_oral_general</t>
+  </si>
+  <si>
+    <t>cost_prep_lenacapavir_agyw</t>
+  </si>
+  <si>
+    <t>cost_prep_lenacapavir_fsw</t>
+  </si>
+  <si>
+    <t>cost_prep_lenacapavir_msm</t>
+  </si>
+  <si>
+    <t>cost_prep_lenacapavir_general</t>
   </si>
 </sst>
 </file>
@@ -559,14 +583,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F954A092-A5F1-D044-85EF-FAF8818A0818}">
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:S45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="33" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>16</v>
       </c>
@@ -600,8 +624,32 @@
       <c r="K1" s="5" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -635,8 +683,32 @@
       <c r="K2" s="1">
         <v>1.745331695</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L2">
+        <v>47.811897250000001</v>
+      </c>
+      <c r="M2">
+        <v>48.92286</v>
+      </c>
+      <c r="N2">
+        <v>46.049460000000003</v>
+      </c>
+      <c r="O2">
+        <v>47.811897250000001</v>
+      </c>
+      <c r="P2">
+        <v>40.768770000000004</v>
+      </c>
+      <c r="Q2">
+        <v>40.768770000000004</v>
+      </c>
+      <c r="R2">
+        <v>38.450769999999999</v>
+      </c>
+      <c r="S2">
+        <v>40.768770000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -670,8 +742,32 @@
       <c r="K3" s="1">
         <v>2.8419164619999999</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L3">
+        <v>54.87190983</v>
+      </c>
+      <c r="M3">
+        <v>56.146920000000001</v>
+      </c>
+      <c r="N3">
+        <v>52.849220000000003</v>
+      </c>
+      <c r="O3">
+        <v>54.87190983</v>
+      </c>
+      <c r="P3">
+        <v>44.06174</v>
+      </c>
+      <c r="Q3">
+        <v>44.06174</v>
+      </c>
+      <c r="R3">
+        <v>41.743740000000003</v>
+      </c>
+      <c r="S3">
+        <v>44.06174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -705,8 +801,32 @@
       <c r="K4" s="1">
         <v>3.5922113019999999</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L4">
+        <v>59.702444749999998</v>
+      </c>
+      <c r="M4">
+        <v>61.089700000000001</v>
+      </c>
+      <c r="N4">
+        <v>57.5017</v>
+      </c>
+      <c r="O4">
+        <v>59.702444749999998</v>
+      </c>
+      <c r="P4">
+        <v>46.314819999999997</v>
+      </c>
+      <c r="Q4">
+        <v>46.314819999999997</v>
+      </c>
+      <c r="R4">
+        <v>43.99682</v>
+      </c>
+      <c r="S4">
+        <v>46.314819999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -740,8 +860,32 @@
       <c r="K5" s="1">
         <v>1.743341523</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L5">
+        <v>47.79908416</v>
+      </c>
+      <c r="M5">
+        <v>48.909750000000003</v>
+      </c>
+      <c r="N5">
+        <v>46.037120000000002</v>
+      </c>
+      <c r="O5">
+        <v>47.79908416</v>
+      </c>
+      <c r="P5">
+        <v>40.762790000000003</v>
+      </c>
+      <c r="Q5">
+        <v>40.762790000000003</v>
+      </c>
+      <c r="R5">
+        <v>38.444789999999998</v>
+      </c>
+      <c r="S5">
+        <v>40.762790000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -775,8 +919,32 @@
       <c r="K6" s="1">
         <v>2.5533415229999998</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L6">
+        <v>53.014011789999998</v>
+      </c>
+      <c r="M6">
+        <v>54.245849999999997</v>
+      </c>
+      <c r="N6">
+        <v>51.059809999999999</v>
+      </c>
+      <c r="O6">
+        <v>53.014011789999998</v>
+      </c>
+      <c r="P6">
+        <v>43.195169999999997</v>
+      </c>
+      <c r="Q6">
+        <v>43.195169999999997</v>
+      </c>
+      <c r="R6">
+        <v>40.87717</v>
+      </c>
+      <c r="S6">
+        <v>43.195169999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -810,8 +978,32 @@
       <c r="K7" s="1">
         <v>2.3782063880000002</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L7">
+        <v>51.886459870000003</v>
+      </c>
+      <c r="M7">
+        <v>53.092100000000002</v>
+      </c>
+      <c r="N7">
+        <v>49.973820000000003</v>
+      </c>
+      <c r="O7">
+        <v>51.886459870000003</v>
+      </c>
+      <c r="P7">
+        <v>42.669249999999998</v>
+      </c>
+      <c r="Q7">
+        <v>42.669249999999998</v>
+      </c>
+      <c r="R7">
+        <v>40.35125</v>
+      </c>
+      <c r="S7">
+        <v>42.669249999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -845,8 +1037,32 @@
       <c r="K8" s="1">
         <v>1.424914005</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L8">
+        <v>45.748989770000001</v>
+      </c>
+      <c r="M8">
+        <v>46.812019999999997</v>
+      </c>
+      <c r="N8">
+        <v>44.06259</v>
+      </c>
+      <c r="O8">
+        <v>45.748989770000001</v>
+      </c>
+      <c r="P8">
+        <v>39.806570000000001</v>
+      </c>
+      <c r="Q8">
+        <v>39.806570000000001</v>
+      </c>
+      <c r="R8">
+        <v>37.488570000000003</v>
+      </c>
+      <c r="S8">
+        <v>39.806570000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -880,8 +1096,32 @@
       <c r="K9" s="1">
         <v>1.2099754300000001</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L9">
+        <v>44.365176050000002</v>
+      </c>
+      <c r="M9">
+        <v>45.396050000000002</v>
+      </c>
+      <c r="N9">
+        <v>42.729790000000001</v>
+      </c>
+      <c r="O9">
+        <v>44.365176050000002</v>
+      </c>
+      <c r="P9">
+        <v>39.16113</v>
+      </c>
+      <c r="Q9">
+        <v>39.16113</v>
+      </c>
+      <c r="R9">
+        <v>36.843130000000002</v>
+      </c>
+      <c r="S9">
+        <v>39.16113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -915,8 +1155,32 @@
       <c r="K10" s="1">
         <v>1.1562407859999999</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L10">
+        <v>44.019222620000001</v>
+      </c>
+      <c r="M10">
+        <v>45.042059999999999</v>
+      </c>
+      <c r="N10">
+        <v>42.396590000000003</v>
+      </c>
+      <c r="O10">
+        <v>44.019222620000001</v>
+      </c>
+      <c r="P10">
+        <v>38.999769999999998</v>
+      </c>
+      <c r="Q10">
+        <v>38.999769999999998</v>
+      </c>
+      <c r="R10">
+        <v>36.68177</v>
+      </c>
+      <c r="S10">
+        <v>38.999769999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
@@ -950,8 +1214,32 @@
       <c r="K11" s="1">
         <v>1.154250614</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L11">
+        <v>44.006409529999999</v>
+      </c>
+      <c r="M11">
+        <v>45.028950000000002</v>
+      </c>
+      <c r="N11">
+        <v>42.384250000000002</v>
+      </c>
+      <c r="O11">
+        <v>44.006409529999999</v>
+      </c>
+      <c r="P11">
+        <v>38.993789999999997</v>
+      </c>
+      <c r="Q11">
+        <v>38.993789999999997</v>
+      </c>
+      <c r="R11">
+        <v>36.675789999999999</v>
+      </c>
+      <c r="S11">
+        <v>38.993789999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -985,8 +1273,32 @@
       <c r="K12" s="1">
         <v>3.3474201469999998</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L12">
+        <v>58.126434690000004</v>
+      </c>
+      <c r="M12">
+        <v>59.477069999999998</v>
+      </c>
+      <c r="N12">
+        <v>55.983780000000003</v>
+      </c>
+      <c r="O12">
+        <v>58.126434690000004</v>
+      </c>
+      <c r="P12">
+        <v>45.579729999999998</v>
+      </c>
+      <c r="Q12">
+        <v>45.579729999999998</v>
+      </c>
+      <c r="R12">
+        <v>43.26173</v>
+      </c>
+      <c r="S12">
+        <v>45.579729999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
@@ -1020,8 +1332,32 @@
       <c r="K13" s="1">
         <v>1.673685504</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L13">
+        <v>47.350626009999999</v>
+      </c>
+      <c r="M13">
+        <v>48.450870000000002</v>
+      </c>
+      <c r="N13">
+        <v>45.60519</v>
+      </c>
+      <c r="O13">
+        <v>47.350626009999999</v>
+      </c>
+      <c r="P13">
+        <v>40.553620000000002</v>
+      </c>
+      <c r="Q13">
+        <v>40.553620000000002</v>
+      </c>
+      <c r="R13">
+        <v>38.235619999999997</v>
+      </c>
+      <c r="S13">
+        <v>40.553620000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
@@ -1055,8 +1391,32 @@
       <c r="K14" s="1">
         <v>3.8131740000000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L14">
+        <v>62.585389999999997</v>
+      </c>
+      <c r="M14">
+        <v>64.039630000000002</v>
+      </c>
+      <c r="N14">
+        <v>60.278370000000002</v>
+      </c>
+      <c r="O14">
+        <v>62.585389999999997</v>
+      </c>
+      <c r="P14">
+        <v>47.659500000000001</v>
+      </c>
+      <c r="Q14">
+        <v>47.659500000000001</v>
+      </c>
+      <c r="R14">
+        <v>45.341500000000003</v>
+      </c>
+      <c r="S14">
+        <v>47.659500000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
@@ -1090,8 +1450,32 @@
       <c r="K15" s="1">
         <v>1.6219410320000001</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L15">
+        <v>47.017485669999999</v>
+      </c>
+      <c r="M15">
+        <v>48.109990000000003</v>
+      </c>
+      <c r="N15">
+        <v>45.284329999999997</v>
+      </c>
+      <c r="O15">
+        <v>47.017485669999999</v>
+      </c>
+      <c r="P15">
+        <v>40.398229999999998</v>
+      </c>
+      <c r="Q15">
+        <v>40.398229999999998</v>
+      </c>
+      <c r="R15">
+        <v>38.08023</v>
+      </c>
+      <c r="S15">
+        <v>40.398229999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
@@ -1125,8 +1509,32 @@
       <c r="K16" s="1">
         <v>2.425970516</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L16">
+        <v>52.19397403</v>
+      </c>
+      <c r="M16">
+        <v>53.406759999999998</v>
+      </c>
+      <c r="N16">
+        <v>50.27</v>
+      </c>
+      <c r="O16">
+        <v>52.19397403</v>
+      </c>
+      <c r="P16">
+        <v>42.81268</v>
+      </c>
+      <c r="Q16">
+        <v>42.81268</v>
+      </c>
+      <c r="R16">
+        <v>40.494680000000002</v>
+      </c>
+      <c r="S16">
+        <v>42.81268</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
@@ -1160,8 +1568,32 @@
       <c r="K17" s="1">
         <v>5.1863390660000004</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L17">
+        <v>69.965729830000001</v>
+      </c>
+      <c r="M17">
+        <v>71.591459999999998</v>
+      </c>
+      <c r="N17">
+        <v>67.386660000000006</v>
+      </c>
+      <c r="O17">
+        <v>69.965729830000001</v>
+      </c>
+      <c r="P17">
+        <v>51.101880000000001</v>
+      </c>
+      <c r="Q17">
+        <v>51.101880000000001</v>
+      </c>
+      <c r="R17">
+        <v>48.783880000000003</v>
+      </c>
+      <c r="S17">
+        <v>51.101880000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -1195,8 +1627,32 @@
       <c r="K18" s="1">
         <v>2.525479115</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L18">
+        <v>52.834628530000003</v>
+      </c>
+      <c r="M18">
+        <v>54.0623</v>
+      </c>
+      <c r="N18">
+        <v>50.887039999999999</v>
+      </c>
+      <c r="O18">
+        <v>52.834628530000003</v>
+      </c>
+      <c r="P18">
+        <v>43.111499999999999</v>
+      </c>
+      <c r="Q18">
+        <v>43.111499999999999</v>
+      </c>
+      <c r="R18">
+        <v>40.793500000000002</v>
+      </c>
+      <c r="S18">
+        <v>43.111499999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -1230,8 +1686,32 @@
       <c r="K19" s="1">
         <v>2.788181818</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="L19">
+        <v>54.525956399999998</v>
+      </c>
+      <c r="M19">
+        <v>55.792929999999998</v>
+      </c>
+      <c r="N19">
+        <v>52.516019999999997</v>
+      </c>
+      <c r="O19">
+        <v>54.525956399999998</v>
+      </c>
+      <c r="P19">
+        <v>43.900379999999998</v>
+      </c>
+      <c r="Q19">
+        <v>43.900379999999998</v>
+      </c>
+      <c r="R19">
+        <v>41.582380000000001</v>
+      </c>
+      <c r="S19">
+        <v>43.900379999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -1265,20 +1745,44 @@
       <c r="K20" s="1">
         <v>1.7174692869999999</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L20">
+        <v>47.63251399</v>
+      </c>
+      <c r="M20">
+        <v>48.739310000000003</v>
+      </c>
+      <c r="N20">
+        <v>45.876690000000004</v>
+      </c>
+      <c r="O20">
+        <v>47.63251399</v>
+      </c>
+      <c r="P20">
+        <v>40.685099999999998</v>
+      </c>
+      <c r="Q20">
+        <v>40.685099999999998</v>
+      </c>
+      <c r="R20">
+        <v>38.367100000000001</v>
+      </c>
+      <c r="S20">
+        <v>40.685099999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -1286,7 +1790,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -1294,7 +1798,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -1302,7 +1806,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -1310,7 +1814,7 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -1318,7 +1822,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -1326,7 +1830,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -1334,7 +1838,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -1342,7 +1846,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>

--- a/data/tier_app/country_costs.xlsx
+++ b/data/tier_app/country_costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/tier_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="8_{A44B6979-C974-2F43-A899-180A4F7BAE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{973E1F22-1C3A-CF44-9E4C-A28B3EC62C24}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{A44B6979-C974-2F43-A899-180A4F7BAE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20931531-4C3C-634E-B56E-47E6B36AC622}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="600" windowWidth="27640" windowHeight="15280" xr2:uid="{A508B7DC-02AE-4845-B676-FDD92F1561DC}"/>
+    <workbookView xWindow="-32700" yWindow="560" windowWidth="27640" windowHeight="15280" xr2:uid="{A508B7DC-02AE-4845-B676-FDD92F1561DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -264,6 +264,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -683,17 +687,17 @@
       <c r="K2" s="1">
         <v>1.745331695</v>
       </c>
-      <c r="L2">
-        <v>47.811897250000001</v>
-      </c>
-      <c r="M2">
-        <v>48.92286</v>
-      </c>
-      <c r="N2">
-        <v>46.049460000000003</v>
-      </c>
-      <c r="O2">
-        <v>47.811897250000001</v>
+      <c r="L2" s="1">
+        <v>90.724662719999998</v>
+      </c>
+      <c r="M2" s="1">
+        <v>92.133444420000004</v>
+      </c>
+      <c r="N2" s="1">
+        <v>88.217350800000006</v>
+      </c>
+      <c r="O2" s="1">
+        <v>90.38165832</v>
       </c>
       <c r="P2">
         <v>40.768770000000004</v>
@@ -742,17 +746,17 @@
       <c r="K3" s="1">
         <v>2.8419164619999999</v>
       </c>
-      <c r="L3">
-        <v>54.87190983</v>
-      </c>
-      <c r="M3">
-        <v>56.146920000000001</v>
-      </c>
-      <c r="N3">
-        <v>52.849220000000003</v>
-      </c>
-      <c r="O3">
-        <v>54.87190983</v>
+      <c r="L3" s="1">
+        <v>104.12127099999999</v>
+      </c>
+      <c r="M3" s="1">
+        <v>105.7380766</v>
+      </c>
+      <c r="N3" s="1">
+        <v>101.2437238</v>
+      </c>
+      <c r="O3" s="1">
+        <v>103.7276178</v>
       </c>
       <c r="P3">
         <v>44.06174</v>
@@ -801,17 +805,17 @@
       <c r="K4" s="1">
         <v>3.5922113019999999</v>
       </c>
-      <c r="L4">
-        <v>59.702444749999998</v>
-      </c>
-      <c r="M4">
-        <v>61.089700000000001</v>
-      </c>
-      <c r="N4">
-        <v>57.5017</v>
-      </c>
-      <c r="O4">
-        <v>59.702444749999998</v>
+      <c r="L4" s="1">
+        <v>113.28737150000001</v>
+      </c>
+      <c r="M4" s="1">
+        <v>115.0465092</v>
+      </c>
+      <c r="N4" s="1">
+        <v>110.15650530000001</v>
+      </c>
+      <c r="O4" s="1">
+        <v>112.8590638</v>
       </c>
       <c r="P4">
         <v>46.314819999999997</v>
@@ -860,17 +864,17 @@
       <c r="K5" s="1">
         <v>1.743341523</v>
       </c>
-      <c r="L5">
-        <v>47.79908416</v>
-      </c>
-      <c r="M5">
-        <v>48.909750000000003</v>
-      </c>
-      <c r="N5">
-        <v>46.037120000000002</v>
-      </c>
-      <c r="O5">
-        <v>47.79908416</v>
+      <c r="L5" s="1">
+        <v>90.700349459999998</v>
+      </c>
+      <c r="M5" s="1">
+        <v>92.108753620000002</v>
+      </c>
+      <c r="N5" s="1">
+        <v>88.193709470000002</v>
+      </c>
+      <c r="O5" s="1">
+        <v>90.357436980000003</v>
       </c>
       <c r="P5">
         <v>40.762790000000003</v>
@@ -919,17 +923,17 @@
       <c r="K6" s="1">
         <v>2.5533415229999998</v>
       </c>
-      <c r="L6">
-        <v>53.014011789999998</v>
-      </c>
-      <c r="M6">
-        <v>54.245849999999997</v>
-      </c>
-      <c r="N6">
-        <v>51.059809999999999</v>
-      </c>
-      <c r="O6">
-        <v>53.014011789999998</v>
+      <c r="L6" s="1">
+        <v>100.5958478</v>
+      </c>
+      <c r="M6" s="1">
+        <v>102.1579102</v>
+      </c>
+      <c r="N6" s="1">
+        <v>97.815730889999998</v>
+      </c>
+      <c r="O6" s="1">
+        <v>100.21552320000001</v>
       </c>
       <c r="P6">
         <v>43.195169999999997</v>
@@ -978,17 +982,17 @@
       <c r="K7" s="1">
         <v>2.3782063880000002</v>
       </c>
-      <c r="L7">
-        <v>51.886459870000003</v>
-      </c>
-      <c r="M7">
-        <v>53.092100000000002</v>
-      </c>
-      <c r="N7">
-        <v>49.973820000000003</v>
-      </c>
-      <c r="O7">
-        <v>51.886459870000003</v>
+      <c r="L7" s="1">
+        <v>98.456280579999998</v>
+      </c>
+      <c r="M7" s="1">
+        <v>99.98511963</v>
+      </c>
+      <c r="N7" s="1">
+        <v>95.735293830000003</v>
+      </c>
+      <c r="O7" s="1">
+        <v>98.084045119999999</v>
       </c>
       <c r="P7">
         <v>42.669249999999998</v>
@@ -1037,17 +1041,17 @@
       <c r="K8" s="1">
         <v>1.424914005</v>
       </c>
-      <c r="L8">
-        <v>45.748989770000001</v>
-      </c>
-      <c r="M8">
-        <v>46.812019999999997</v>
-      </c>
-      <c r="N8">
-        <v>44.06259</v>
-      </c>
-      <c r="O8">
-        <v>45.748989770000001</v>
+      <c r="L8" s="1">
+        <v>86.810227260000005</v>
+      </c>
+      <c r="M8" s="1">
+        <v>88.158225220000006</v>
+      </c>
+      <c r="N8" s="1">
+        <v>84.411096630000003</v>
+      </c>
+      <c r="O8" s="1">
+        <v>86.482022240000006</v>
       </c>
       <c r="P8">
         <v>39.806570000000001</v>
@@ -1096,17 +1100,17 @@
       <c r="K9" s="1">
         <v>1.2099754300000001</v>
       </c>
-      <c r="L9">
-        <v>44.365176050000002</v>
-      </c>
-      <c r="M9">
-        <v>45.396050000000002</v>
-      </c>
-      <c r="N9">
-        <v>42.729790000000001</v>
-      </c>
-      <c r="O9">
-        <v>44.365176050000002</v>
+      <c r="L9" s="1">
+        <v>84.184394780000005</v>
+      </c>
+      <c r="M9" s="1">
+        <v>85.491618540000005</v>
+      </c>
+      <c r="N9" s="1">
+        <v>81.857832959999996</v>
+      </c>
+      <c r="O9" s="1">
+        <v>83.866117290000005</v>
       </c>
       <c r="P9">
         <v>39.16113</v>
@@ -1155,17 +1159,17 @@
       <c r="K10" s="1">
         <v>1.1562407859999999</v>
       </c>
-      <c r="L10">
-        <v>44.019222620000001</v>
-      </c>
-      <c r="M10">
-        <v>45.042059999999999</v>
-      </c>
-      <c r="N10">
-        <v>42.396590000000003</v>
-      </c>
-      <c r="O10">
-        <v>44.019222620000001</v>
+      <c r="L10" s="1">
+        <v>83.527936659999995</v>
+      </c>
+      <c r="M10" s="1">
+        <v>84.824966869999997</v>
+      </c>
+      <c r="N10" s="1">
+        <v>81.219517039999999</v>
+      </c>
+      <c r="O10" s="1">
+        <v>83.212141059999993</v>
       </c>
       <c r="P10">
         <v>38.999769999999998</v>
@@ -1214,17 +1218,17 @@
       <c r="K11" s="1">
         <v>1.154250614</v>
       </c>
-      <c r="L11">
-        <v>44.006409529999999</v>
-      </c>
-      <c r="M11">
-        <v>45.028950000000002</v>
-      </c>
-      <c r="N11">
-        <v>42.384250000000002</v>
-      </c>
-      <c r="O11">
-        <v>44.006409529999999</v>
+      <c r="L11" s="1">
+        <v>83.503623399999995</v>
+      </c>
+      <c r="M11" s="1">
+        <v>84.800276069999995</v>
+      </c>
+      <c r="N11" s="1">
+        <v>81.195875709999996</v>
+      </c>
+      <c r="O11" s="1">
+        <v>83.187919719999996</v>
       </c>
       <c r="P11">
         <v>38.993789999999997</v>
@@ -1273,17 +1277,17 @@
       <c r="K12" s="1">
         <v>3.3474201469999998</v>
       </c>
-      <c r="L12">
-        <v>58.126434690000004</v>
-      </c>
-      <c r="M12">
-        <v>59.477069999999998</v>
-      </c>
-      <c r="N12">
-        <v>55.983780000000003</v>
-      </c>
-      <c r="O12">
-        <v>58.126434690000004</v>
+      <c r="L12" s="1">
+        <v>110.29684</v>
+      </c>
+      <c r="M12" s="1">
+        <v>112.0095405</v>
+      </c>
+      <c r="N12" s="1">
+        <v>107.2486217</v>
+      </c>
+      <c r="O12" s="1">
+        <v>109.87983869999999</v>
       </c>
       <c r="P12">
         <v>45.579729999999998</v>
@@ -1332,17 +1336,17 @@
       <c r="K13" s="1">
         <v>1.673685504</v>
       </c>
-      <c r="L13">
-        <v>47.350626009999999</v>
-      </c>
-      <c r="M13">
-        <v>48.450870000000002</v>
-      </c>
-      <c r="N13">
-        <v>45.60519</v>
-      </c>
-      <c r="O13">
-        <v>47.350626009999999</v>
+      <c r="L13" s="1">
+        <v>89.849385229999996</v>
+      </c>
+      <c r="M13" s="1">
+        <v>91.244575530000006</v>
+      </c>
+      <c r="N13" s="1">
+        <v>87.366262910000003</v>
+      </c>
+      <c r="O13" s="1">
+        <v>89.50969001</v>
       </c>
       <c r="P13">
         <v>40.553620000000002</v>
@@ -1391,17 +1395,17 @@
       <c r="K14" s="1">
         <v>3.8131740000000001</v>
       </c>
-      <c r="L14">
-        <v>62.585389999999997</v>
-      </c>
-      <c r="M14">
-        <v>64.039630000000002</v>
-      </c>
-      <c r="N14">
-        <v>60.278370000000002</v>
-      </c>
-      <c r="O14">
-        <v>62.585389999999997</v>
+      <c r="L14" s="1">
+        <v>118.7578558</v>
+      </c>
+      <c r="M14" s="1">
+        <v>120.6019397</v>
+      </c>
+      <c r="N14" s="1">
+        <v>115.4758046</v>
+      </c>
+      <c r="O14" s="1">
+        <v>118.30886580000001</v>
       </c>
       <c r="P14">
         <v>47.659500000000001</v>
@@ -1450,17 +1454,17 @@
       <c r="K15" s="1">
         <v>1.6219410320000001</v>
       </c>
-      <c r="L15">
-        <v>47.017485669999999</v>
-      </c>
-      <c r="M15">
-        <v>48.109990000000003</v>
-      </c>
-      <c r="N15">
-        <v>45.284329999999997</v>
-      </c>
-      <c r="O15">
-        <v>47.017485669999999</v>
+      <c r="L15" s="1">
+        <v>89.217240369999999</v>
+      </c>
+      <c r="M15" s="1">
+        <v>90.602614669999994</v>
+      </c>
+      <c r="N15" s="1">
+        <v>86.751588319999996</v>
+      </c>
+      <c r="O15" s="1">
+        <v>88.879935110000005</v>
       </c>
       <c r="P15">
         <v>40.398229999999998</v>
@@ -1509,17 +1513,17 @@
       <c r="K16" s="1">
         <v>2.425970516</v>
       </c>
-      <c r="L16">
-        <v>52.19397403</v>
-      </c>
-      <c r="M16">
-        <v>53.406759999999998</v>
-      </c>
-      <c r="N16">
-        <v>50.27</v>
-      </c>
-      <c r="O16">
-        <v>52.19397403</v>
+      <c r="L16" s="1">
+        <v>99.039798910000002</v>
+      </c>
+      <c r="M16" s="1">
+        <v>100.5776989</v>
+      </c>
+      <c r="N16" s="1">
+        <v>96.302685749999995</v>
+      </c>
+      <c r="O16" s="1">
+        <v>98.665357330000006</v>
       </c>
       <c r="P16">
         <v>42.81268</v>
@@ -1568,17 +1572,17 @@
       <c r="K17" s="1">
         <v>5.1863390660000004</v>
       </c>
-      <c r="L17">
-        <v>69.965729830000001</v>
-      </c>
-      <c r="M17">
-        <v>71.591459999999998</v>
-      </c>
-      <c r="N17">
-        <v>67.386660000000006</v>
-      </c>
-      <c r="O17">
-        <v>69.965729830000001</v>
+      <c r="L17" s="1">
+        <v>132.76229570000001</v>
+      </c>
+      <c r="M17" s="1">
+        <v>134.82384200000001</v>
+      </c>
+      <c r="N17" s="1">
+        <v>129.09321080000001</v>
+      </c>
+      <c r="O17" s="1">
+        <v>132.26035880000001</v>
       </c>
       <c r="P17">
         <v>51.101880000000001</v>
@@ -1627,17 +1631,17 @@
       <c r="K18" s="1">
         <v>2.525479115</v>
       </c>
-      <c r="L18">
-        <v>52.834628530000003</v>
-      </c>
-      <c r="M18">
-        <v>54.0623</v>
-      </c>
-      <c r="N18">
-        <v>50.887039999999999</v>
-      </c>
-      <c r="O18">
-        <v>52.834628530000003</v>
+      <c r="L18" s="1">
+        <v>100.2554621</v>
+      </c>
+      <c r="M18" s="1">
+        <v>101.81223900000001</v>
+      </c>
+      <c r="N18" s="1">
+        <v>97.484752270000001</v>
+      </c>
+      <c r="O18" s="1">
+        <v>99.87642443</v>
       </c>
       <c r="P18">
         <v>43.111499999999999</v>
@@ -1686,17 +1690,17 @@
       <c r="K19" s="1">
         <v>2.788181818</v>
       </c>
-      <c r="L19">
-        <v>54.525956399999998</v>
-      </c>
-      <c r="M19">
-        <v>55.792929999999998</v>
-      </c>
-      <c r="N19">
-        <v>52.516019999999997</v>
-      </c>
-      <c r="O19">
-        <v>54.525956399999998</v>
+      <c r="L19" s="1">
+        <v>103.4648129</v>
+      </c>
+      <c r="M19" s="1">
+        <v>105.0714249</v>
+      </c>
+      <c r="N19" s="1">
+        <v>100.6054079</v>
+      </c>
+      <c r="O19" s="1">
+        <v>103.0736416</v>
       </c>
       <c r="P19">
         <v>43.900379999999998</v>
@@ -1745,17 +1749,17 @@
       <c r="K20" s="1">
         <v>1.7174692869999999</v>
       </c>
-      <c r="L20">
-        <v>47.63251399</v>
-      </c>
-      <c r="M20">
-        <v>48.739310000000003</v>
-      </c>
-      <c r="N20">
-        <v>45.876690000000004</v>
-      </c>
-      <c r="O20">
-        <v>47.63251399</v>
+      <c r="L20" s="1">
+        <v>90.384277030000007</v>
+      </c>
+      <c r="M20" s="1">
+        <v>91.787773189999996</v>
+      </c>
+      <c r="N20" s="1">
+        <v>87.886372179999995</v>
+      </c>
+      <c r="O20" s="1">
+        <v>90.042559530000005</v>
       </c>
       <c r="P20">
         <v>40.685099999999998</v>

--- a/data/tier_app/country_costs.xlsx
+++ b/data/tier_app/country_costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/tier_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{A44B6979-C974-2F43-A899-180A4F7BAE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20931531-4C3C-634E-B56E-47E6B36AC622}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="8_{A44B6979-C974-2F43-A899-180A4F7BAE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FF0585A-C3AA-0244-9D44-6CFD2623BE7B}"/>
   <bookViews>
-    <workbookView xWindow="-32700" yWindow="560" windowWidth="27640" windowHeight="15280" xr2:uid="{A508B7DC-02AE-4845-B676-FDD92F1561DC}"/>
+    <workbookView xWindow="120" yWindow="600" windowWidth="27640" windowHeight="15280" xr2:uid="{A508B7DC-02AE-4845-B676-FDD92F1561DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -264,10 +264,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -699,17 +695,17 @@
       <c r="O2" s="1">
         <v>90.38165832</v>
       </c>
-      <c r="P2">
-        <v>40.768770000000004</v>
-      </c>
-      <c r="Q2">
-        <v>40.768770000000004</v>
-      </c>
-      <c r="R2">
-        <v>38.450769999999999</v>
-      </c>
-      <c r="S2">
-        <v>40.768770000000004</v>
+      <c r="P2" s="1">
+        <v>51.878401109999999</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>51.878401109999999</v>
+      </c>
+      <c r="R2" s="1">
+        <v>49.377401110000001</v>
+      </c>
+      <c r="S2" s="1">
+        <v>51.878401109999999</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="17" x14ac:dyDescent="0.2">
@@ -758,17 +754,17 @@
       <c r="O3" s="1">
         <v>103.7276178</v>
       </c>
-      <c r="P3">
-        <v>44.06174</v>
-      </c>
-      <c r="Q3">
-        <v>44.06174</v>
-      </c>
-      <c r="R3">
-        <v>41.743740000000003</v>
-      </c>
-      <c r="S3">
-        <v>44.06174</v>
+      <c r="P3" s="1">
+        <v>55.821706390000003</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>55.821706390000003</v>
+      </c>
+      <c r="R3" s="1">
+        <v>53.320706389999998</v>
+      </c>
+      <c r="S3" s="1">
+        <v>55.821706390000003</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="17" x14ac:dyDescent="0.2">
@@ -817,17 +813,17 @@
       <c r="O4" s="1">
         <v>112.8590638</v>
       </c>
-      <c r="P4">
-        <v>46.314819999999997</v>
-      </c>
-      <c r="Q4">
-        <v>46.314819999999997</v>
-      </c>
-      <c r="R4">
-        <v>43.99682</v>
-      </c>
-      <c r="S4">
-        <v>46.314819999999997</v>
+      <c r="P4" s="1">
+        <v>58.519757370000001</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>58.519757370000001</v>
+      </c>
+      <c r="R4" s="1">
+        <v>56.018757370000003</v>
+      </c>
+      <c r="S4" s="1">
+        <v>58.519757370000001</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="17" x14ac:dyDescent="0.2">
@@ -876,17 +872,17 @@
       <c r="O5" s="1">
         <v>90.357436980000003</v>
       </c>
-      <c r="P5">
-        <v>40.762790000000003</v>
-      </c>
-      <c r="Q5">
-        <v>40.762790000000003</v>
-      </c>
-      <c r="R5">
-        <v>38.444789999999998</v>
-      </c>
-      <c r="S5">
-        <v>40.762790000000003</v>
+      <c r="P5" s="1">
+        <v>51.871244470000001</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>51.871244470000001</v>
+      </c>
+      <c r="R5" s="1">
+        <v>49.370244470000003</v>
+      </c>
+      <c r="S5" s="1">
+        <v>51.871244470000001</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="17" x14ac:dyDescent="0.2">
@@ -935,17 +931,17 @@
       <c r="O6" s="1">
         <v>100.21552320000001</v>
       </c>
-      <c r="P6">
-        <v>43.195169999999997</v>
-      </c>
-      <c r="Q6">
-        <v>43.195169999999997</v>
-      </c>
-      <c r="R6">
-        <v>40.87717</v>
-      </c>
-      <c r="S6">
-        <v>43.195169999999997</v>
+      <c r="P6" s="1">
+        <v>54.783994470000003</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>54.783994470000003</v>
+      </c>
+      <c r="R6" s="1">
+        <v>52.282994469999998</v>
+      </c>
+      <c r="S6" s="1">
+        <v>54.783994470000003</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="17" x14ac:dyDescent="0.2">
@@ -994,17 +990,17 @@
       <c r="O7" s="1">
         <v>98.084045119999999</v>
       </c>
-      <c r="P7">
-        <v>42.669249999999998</v>
-      </c>
-      <c r="Q7">
-        <v>42.669249999999998</v>
-      </c>
-      <c r="R7">
-        <v>40.35125</v>
-      </c>
-      <c r="S7">
-        <v>42.669249999999998</v>
+      <c r="P7" s="1">
+        <v>54.154210689999999</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>54.154210689999999</v>
+      </c>
+      <c r="R7" s="1">
+        <v>51.653210690000002</v>
+      </c>
+      <c r="S7" s="1">
+        <v>54.154210689999999</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="17" x14ac:dyDescent="0.2">
@@ -1053,17 +1049,17 @@
       <c r="O8" s="1">
         <v>86.482022240000006</v>
       </c>
-      <c r="P8">
-        <v>39.806570000000001</v>
-      </c>
-      <c r="Q8">
-        <v>39.806570000000001</v>
-      </c>
-      <c r="R8">
-        <v>37.488570000000003</v>
-      </c>
-      <c r="S8">
-        <v>39.806570000000001</v>
+      <c r="P8" s="1">
+        <v>50.726183050000003</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>50.726183050000003</v>
+      </c>
+      <c r="R8" s="1">
+        <v>48.225183049999998</v>
+      </c>
+      <c r="S8" s="1">
+        <v>50.726183050000003</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="17" x14ac:dyDescent="0.2">
@@ -1112,17 +1108,17 @@
       <c r="O9" s="1">
         <v>83.866117290000005</v>
       </c>
-      <c r="P9">
-        <v>39.16113</v>
-      </c>
-      <c r="Q9">
-        <v>39.16113</v>
-      </c>
-      <c r="R9">
-        <v>36.843130000000002</v>
-      </c>
-      <c r="S9">
-        <v>39.16113</v>
+      <c r="P9" s="1">
+        <v>49.953266579999998</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>49.953266579999998</v>
+      </c>
+      <c r="R9" s="1">
+        <v>47.45226658</v>
+      </c>
+      <c r="S9" s="1">
+        <v>49.953266579999998</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="17" x14ac:dyDescent="0.2">
@@ -1171,17 +1167,17 @@
       <c r="O10" s="1">
         <v>83.212141059999993</v>
       </c>
-      <c r="P10">
-        <v>38.999769999999998</v>
-      </c>
-      <c r="Q10">
-        <v>38.999769999999998</v>
-      </c>
-      <c r="R10">
-        <v>36.68177</v>
-      </c>
-      <c r="S10">
-        <v>38.999769999999998</v>
+      <c r="P10" s="1">
+        <v>49.76003747</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>49.76003747</v>
+      </c>
+      <c r="R10" s="1">
+        <v>47.259037470000003</v>
+      </c>
+      <c r="S10" s="1">
+        <v>49.76003747</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="17" x14ac:dyDescent="0.2">
@@ -1230,17 +1226,17 @@
       <c r="O11" s="1">
         <v>83.187919719999996</v>
       </c>
-      <c r="P11">
-        <v>38.993789999999997</v>
-      </c>
-      <c r="Q11">
-        <v>38.993789999999997</v>
-      </c>
-      <c r="R11">
-        <v>36.675789999999999</v>
-      </c>
-      <c r="S11">
-        <v>38.993789999999997</v>
+      <c r="P11" s="1">
+        <v>49.752880840000003</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>49.752880840000003</v>
+      </c>
+      <c r="R11" s="1">
+        <v>47.251880839999998</v>
+      </c>
+      <c r="S11" s="1">
+        <v>49.752880840000003</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="17" x14ac:dyDescent="0.2">
@@ -1289,17 +1285,17 @@
       <c r="O12" s="1">
         <v>109.87983869999999</v>
       </c>
-      <c r="P12">
-        <v>45.579729999999998</v>
-      </c>
-      <c r="Q12">
-        <v>45.579729999999998</v>
-      </c>
-      <c r="R12">
-        <v>43.26173</v>
-      </c>
-      <c r="S12">
-        <v>45.579729999999998</v>
+      <c r="P12" s="1">
+        <v>57.639491399999997</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>57.639491399999997</v>
+      </c>
+      <c r="R12" s="1">
+        <v>55.138491399999999</v>
+      </c>
+      <c r="S12" s="1">
+        <v>57.639491399999997</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="17" x14ac:dyDescent="0.2">
@@ -1348,17 +1344,17 @@
       <c r="O13" s="1">
         <v>89.50969001</v>
       </c>
-      <c r="P13">
-        <v>40.553620000000002</v>
-      </c>
-      <c r="Q13">
-        <v>40.553620000000002</v>
-      </c>
-      <c r="R13">
-        <v>38.235619999999997</v>
-      </c>
-      <c r="S13">
-        <v>40.553620000000002</v>
+      <c r="P13" s="1">
+        <v>51.620762290000002</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>51.620762290000002</v>
+      </c>
+      <c r="R13" s="1">
+        <v>49.119762289999997</v>
+      </c>
+      <c r="S13" s="1">
+        <v>51.620762290000002</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="17" x14ac:dyDescent="0.2">
@@ -1407,17 +1403,17 @@
       <c r="O14" s="1">
         <v>118.30886580000001</v>
       </c>
-      <c r="P14">
-        <v>47.659500000000001</v>
-      </c>
-      <c r="Q14">
-        <v>47.659500000000001</v>
-      </c>
-      <c r="R14">
-        <v>45.341500000000003</v>
-      </c>
-      <c r="S14">
-        <v>47.659500000000001</v>
+      <c r="P14" s="1">
+        <v>60.13</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>60.13</v>
+      </c>
+      <c r="R14" s="1">
+        <v>57.628999999999998</v>
+      </c>
+      <c r="S14" s="1">
+        <v>60.13</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="17" x14ac:dyDescent="0.2">
@@ -1466,17 +1462,17 @@
       <c r="O15" s="1">
         <v>88.879935110000005</v>
       </c>
-      <c r="P15">
-        <v>40.398229999999998</v>
-      </c>
-      <c r="Q15">
-        <v>40.398229999999998</v>
-      </c>
-      <c r="R15">
-        <v>38.08023</v>
-      </c>
-      <c r="S15">
-        <v>40.398229999999998</v>
+      <c r="P15" s="1">
+        <v>51.434689800000001</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>51.434689800000001</v>
+      </c>
+      <c r="R15" s="1">
+        <v>48.933689800000003</v>
+      </c>
+      <c r="S15" s="1">
+        <v>51.434689800000001</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="17" x14ac:dyDescent="0.2">
@@ -1525,17 +1521,17 @@
       <c r="O16" s="1">
         <v>98.665357330000006</v>
       </c>
-      <c r="P16">
-        <v>42.81268</v>
-      </c>
-      <c r="Q16">
-        <v>42.81268</v>
-      </c>
-      <c r="R16">
-        <v>40.494680000000002</v>
-      </c>
-      <c r="S16">
-        <v>42.81268</v>
+      <c r="P16" s="1">
+        <v>54.325969899999997</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>54.325969899999997</v>
+      </c>
+      <c r="R16" s="1">
+        <v>51.824969899999999</v>
+      </c>
+      <c r="S16" s="1">
+        <v>54.325969899999997</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="17" x14ac:dyDescent="0.2">
@@ -1584,17 +1580,17 @@
       <c r="O17" s="1">
         <v>132.26035880000001</v>
       </c>
-      <c r="P17">
-        <v>51.101880000000001</v>
-      </c>
-      <c r="Q17">
-        <v>51.101880000000001</v>
-      </c>
-      <c r="R17">
-        <v>48.783880000000003</v>
-      </c>
-      <c r="S17">
-        <v>51.101880000000001</v>
+      <c r="P17" s="1">
+        <v>64.252221129999995</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>64.252221129999995</v>
+      </c>
+      <c r="R17" s="1">
+        <v>61.751221129999998</v>
+      </c>
+      <c r="S17" s="1">
+        <v>64.252221129999995</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="17" x14ac:dyDescent="0.2">
@@ -1643,17 +1639,17 @@
       <c r="O18" s="1">
         <v>99.87642443</v>
       </c>
-      <c r="P18">
-        <v>43.111499999999999</v>
-      </c>
-      <c r="Q18">
-        <v>43.111499999999999</v>
-      </c>
-      <c r="R18">
-        <v>40.793500000000002</v>
-      </c>
-      <c r="S18">
-        <v>43.111499999999999</v>
+      <c r="P18" s="1">
+        <v>54.683801600000002</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>54.683801600000002</v>
+      </c>
+      <c r="R18" s="1">
+        <v>52.182801599999998</v>
+      </c>
+      <c r="S18" s="1">
+        <v>54.683801600000002</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="17" x14ac:dyDescent="0.2">
@@ -1702,17 +1698,17 @@
       <c r="O19" s="1">
         <v>103.0736416</v>
       </c>
-      <c r="P19">
-        <v>43.900379999999998</v>
-      </c>
-      <c r="Q19">
-        <v>43.900379999999998</v>
-      </c>
-      <c r="R19">
-        <v>41.582380000000001</v>
-      </c>
-      <c r="S19">
-        <v>43.900379999999998</v>
+      <c r="P19" s="1">
+        <v>55.628477269999998</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>55.628477269999998</v>
+      </c>
+      <c r="R19" s="1">
+        <v>53.12747727</v>
+      </c>
+      <c r="S19" s="1">
+        <v>55.628477269999998</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="34" x14ac:dyDescent="0.2">
@@ -1761,17 +1757,17 @@
       <c r="O20" s="1">
         <v>90.042559530000005</v>
       </c>
-      <c r="P20">
-        <v>40.685099999999998</v>
-      </c>
-      <c r="Q20">
-        <v>40.685099999999998</v>
-      </c>
-      <c r="R20">
-        <v>38.367100000000001</v>
-      </c>
-      <c r="S20">
-        <v>40.685099999999998</v>
+      <c r="P20" s="1">
+        <v>51.778208229999997</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>51.778208229999997</v>
+      </c>
+      <c r="R20" s="1">
+        <v>49.277208229999999</v>
+      </c>
+      <c r="S20" s="1">
+        <v>51.778208229999997</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
